--- a/LISTEN/Script/23_07_n3/23_07.xlsx
+++ b/LISTEN/Script/23_07_n3/23_07.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -485,71 +485,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>翌週</t>
+          <t>故郷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>よくしゅう</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>下周；次周</t>
-        </is>
-      </c>
+          <t>こきょう</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>故郷</t>
+          <t>1泊2日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>こきょう</t>
+          <t>いっぱくふつか</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1泊2日</t>
+          <t>翌週</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>いっぱくふつか</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>よくしゅう</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>下周；次周</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>何日</t>
+          <t>面接</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>なんにち</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>几号；哪一天</t>
-        </is>
-      </c>
+          <t>めんせつ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -557,12 +553,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>説明会</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ざいりょう</t>
+          <t>せつめいかい</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -573,12 +569,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>予想</t>
+          <t>希望</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>よそう</t>
+          <t>きぼう</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -589,15 +585,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>面接</t>
+          <t>何日</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>めんせつ</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>なんにち</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>几号；哪一天</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -605,12 +605,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>説明会</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>せつめいかい</t>
+          <t>ざいりょう</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -621,19 +621,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>表</t>
+          <t>予想</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ひょう</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>表格；图表；表面</t>
-        </is>
-      </c>
+          <t>よそう</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -641,17 +637,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>出席</t>
+          <t>連れる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>しゅっせき</t>
+          <t>つれる</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>出席；参加</t>
+          <t>带领；携带；伴随</t>
         </is>
       </c>
     </row>
@@ -661,17 +657,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>実家</t>
+          <t>表</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>じっか</t>
+          <t>ひょう</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>老家</t>
+          <t>表格；图表；表面</t>
         </is>
       </c>
     </row>
@@ -681,17 +677,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>丁度</t>
+          <t>実家</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ちょうど</t>
+          <t>じっか</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>正好；恰好</t>
+          <t>老家</t>
         </is>
       </c>
     </row>
@@ -753,41 +749,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>書く</t>
+          <t>出席</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>かく</t>
+          <t>しゅっせき</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>写</t>
+          <t>出席；参加</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>都合</t>
+          <t>丁度</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>つごう</t>
+          <t>ちょうど</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>つごう</t>
+          <t>正好；恰好</t>
         </is>
       </c>
     </row>
@@ -797,15 +793,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鶏肉</t>
+          <t>預かる</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>とりにく</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>あずかる</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>保管；存放；照看；管理</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -813,17 +813,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>一人ずつ</t>
+          <t>書く</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ひとりずつ</t>
+          <t>かく</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>逐个；每人</t>
+          <t>写</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>就職試験</t>
+          <t>鶏肉</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>しゅうしょくしけん</t>
+          <t>とりにく</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -849,17 +849,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>多め</t>
+          <t>一人ずつ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>おおめ</t>
+          <t>ひとりずつ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>多一些，略多些</t>
+          <t>逐个；每人</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>パンフレット</t>
+          <t>就職試験</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>宣传册</t>
+          <t>しゅうしょくしけん</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -885,17 +885,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>預かる</t>
+          <t>多め</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>あずかる</t>
+          <t>おおめ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>保管；存放；照看；管理</t>
+          <t>多一些，略多些</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>週末</t>
+          <t>パンフレット</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>しゅうまつ</t>
+          <t>宣传册</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -921,19 +921,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>時期</t>
+          <t>暇な日</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>じき</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>时期；季节；时机</t>
-        </is>
-      </c>
+          <t>ひまなひ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -941,19 +937,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>続ける</t>
+          <t>週末</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>つづける</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>继续；持续；连接</t>
-        </is>
-      </c>
+          <t>しゅうまつ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -961,15 +953,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>暇な日</t>
+          <t>都合</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ひまなひ</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>つごう</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>つごう</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -977,15 +973,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>プリンター</t>
+          <t>続ける</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>打印机</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>つづける</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>继续；持续；连接</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -993,12 +993,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>プリンター</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>えいぎょう</t>
+          <t>打印机</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1009,19 +1009,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>渡す</t>
+          <t>営業</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>わたす</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>传递；交付；授予</t>
-        </is>
-      </c>
+          <t>えいぎょう</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1029,15 +1025,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>希望</t>
+          <t>渡す</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>きぼう</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>わたす</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>传递；交付；授予</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>連れる</t>
+          <t>時期</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>つれる</t>
+          <t>じき</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>带领；携带；伴随</t>
+          <t>时期；季节；时机</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1180,41 +1180,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>流れ</t>
+          <t>蓋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ながれ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>流动；趋势；流程</t>
-        </is>
-      </c>
+          <t>ふた</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>取っ手</t>
+          <t>随分</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>とって</t>
+          <t>ずいぶん</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>把手；手柄</t>
+          <t>相当；非常；很</t>
         </is>
       </c>
     </row>
@@ -1224,15 +1220,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>蓋</t>
+          <t>流れ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ふた</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>ながれ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>流动；趋势；流程</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>随分</t>
+          <t>取っ手</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ずいぶん</t>
+          <t>とって</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>相当；非常；很</t>
+          <t>把手；手柄</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>特に</t>
+          <t>基本的</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>とくに</t>
+          <t>きほんてき</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1308,19 +1308,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>味</t>
+          <t>特に</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>あじ</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>味道；滋味</t>
-        </is>
-      </c>
+          <t>とくに</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1328,15 +1324,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>基本的</t>
+          <t>味</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>きほんてき</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>あじ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>味道；滋味</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1344,19 +1344,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>詰まり</t>
+          <t>野菜</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>つまり</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>总之；也就是说</t>
-        </is>
-      </c>
+          <t>やさい</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1364,15 +1360,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>野菜</t>
+          <t>姉</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>やさい</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>あね</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>姐姐</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>姉</t>
+          <t>詰まり</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>あね</t>
+          <t>つまり</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>姐姐</t>
+          <t>总之；也就是说</t>
         </is>
       </c>
     </row>
@@ -1644,95 +1644,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>減る</t>
+          <t>平仮名</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>へる</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>减少；降低；减轻</t>
-        </is>
-      </c>
+          <t>ひらがな</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>平仮名</t>
+          <t>植える</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ひらがな</t>
+          <t>うえる</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>幸せ</t>
+          <t>穿く</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>しあわせ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>幸福；幸运；好运</t>
-        </is>
-      </c>
+          <t>はく</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>片仮名</t>
+          <t>幸せ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>かたかな</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>しあわせ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>幸福；幸运；好运</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>季節</t>
+          <t>片仮名</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>きせつ</t>
+          <t>かたかな</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1748,35 +1744,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ズボン</t>
+          <t>登山</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>裤子；长裤</t>
+          <t>とざん</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ジーンズ</t>
+          <t>脱ぐ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>ぬぐ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>脱下；脱掉</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>穿く</t>
+          <t>ズボン</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>はく</t>
+          <t>裤子；长裤</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1800,19 +1800,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>脱ぐ</t>
+          <t>季節</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ぬぐ</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>脱下；脱掉</t>
-        </is>
-      </c>
+          <t>きせつ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,17 +1816,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>登る</t>
+          <t>減る</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>のぼる</t>
+          <t>へる</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>攀登；登上</t>
+          <t>减少；降低；减轻</t>
         </is>
       </c>
     </row>
@@ -1840,19 +1836,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ここ数年</t>
+          <t>ジーンズ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ここすうねん</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>近几年；这数年</t>
-        </is>
-      </c>
+          <t>牛仔裤</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1860,17 +1852,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>山登り</t>
+          <t>ここ数年</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>やまのぼり</t>
+          <t>ここすうねん</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>登山；爬山</t>
+          <t>近几年；这数年</t>
         </is>
       </c>
     </row>
@@ -1880,15 +1872,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>登山</t>
+          <t>登る</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>とざん</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>のぼる</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>攀登；登上</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1896,15 +1892,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>植える</t>
+          <t>山登り</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>うえる</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>やまのぼり</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>登山；爬山</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">

--- a/LISTEN/Script/23_07_n3/23_07.xlsx
+++ b/LISTEN/Script/23_07_n3/23_07.xlsx
@@ -1609,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.25" customWidth="1" min="1" max="1"/>
@@ -1641,6 +1641,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1657,6 +1662,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1673,6 +1683,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1689,6 +1704,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1709,6 +1729,11 @@
           <t>幸福；幸运；好运</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1725,6 +1750,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1741,6 +1771,11 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1757,6 +1792,7 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1777,6 +1813,7 @@
           <t>脱下；脱掉</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1793,6 +1830,7 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1809,6 +1847,7 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1868,7 @@
           <t>减少；降低；减轻</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1885,7 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1865,6 +1906,7 @@
           <t>近几年；这数年</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1885,6 +1927,7 @@
           <t>攀登；登上</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1905,6 +1948,7 @@
           <t>登山；爬山</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1921,6 +1965,7 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1937,6 +1982,7 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1957,6 +2003,7 @@
           <t>出生；产生；出现</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1973,6 +2020,7 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1989,6 +2037,7 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2009,6 +2058,7 @@
           <t>赏花；观樱</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2025,6 +2075,7 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2041,6 +2092,7 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2057,6 +2109,7 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2073,6 +2126,7 @@
           <t>到来；来临</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2093,6 +2147,7 @@
           <t>走路方式</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2113,6 +2168,7 @@
           <t>上衣；外套</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2129,6 +2185,7 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2145,6 +2202,7 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2165,6 +2223,7 @@
           <t>后天</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LISTEN/Script/23_07_n3/23_07.xlsx
+++ b/LISTEN/Script/23_07_n3/23_07.xlsx
@@ -1649,7 +1649,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
     </row>
@@ -1706,13 +1706,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1731,13 +1731,13 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1792,7 +1792,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1813,7 +1817,11 @@
           <t>脱下；脱掉</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1830,7 +1838,11 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,11 +1859,15 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1868,7 +1884,11 @@
           <t>减少；降低；减轻</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,7 +1905,11 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1906,11 +1930,15 @@
           <t>近几年；这数年</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1927,7 +1955,11 @@
           <t>攀登；登上</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1948,7 +1980,11 @@
           <t>登山；爬山</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1965,11 +2001,15 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1982,7 +2022,11 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2003,7 +2047,11 @@
           <t>出生；产生；出现</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2020,7 +2068,11 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2037,7 +2089,11 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2058,7 +2114,11 @@
           <t>赏花；观樱</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2075,7 +2135,11 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2092,7 +2156,11 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2109,7 +2177,11 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2126,7 +2198,11 @@
           <t>到来；来临</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2147,7 +2223,11 @@
           <t>走路方式</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2168,7 +2248,11 @@
           <t>上衣；外套</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2185,7 +2269,11 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2202,7 +2290,11 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2223,7 +2315,11 @@
           <t>后天</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
